--- a/___cfiles/副本干洗商品价格表及分成比例.xlsx
+++ b/___cfiles/副本干洗商品价格表及分成比例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17040"/>
+    <workbookView windowHeight="16940"/>
   </bookViews>
   <sheets>
     <sheet name="干洗商品价格表及分成比例" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="105">
   <si>
     <t>品名</t>
   </si>
   <si>
     <t>单价</t>
+  </si>
+  <si>
+    <t>单位</t>
   </si>
   <si>
     <t>工厂</t>
@@ -346,16 +349,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -363,7 +366,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -371,14 +374,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -386,7 +389,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -394,7 +397,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -402,7 +405,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -410,7 +413,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -418,14 +421,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -433,7 +436,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -441,7 +444,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -449,14 +452,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -464,42 +467,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -815,19 +818,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -984,55 +987,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1516,13 +1519,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L102"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="10.3828125" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="21.3173076923077" customWidth="1"/>
-    <col min="5" max="6" width="15.7019230769231" customWidth="1"/>
-    <col min="7" max="8" width="15.7019230769231" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7019230769231" style="2" customWidth="1"/>
-    <col min="11" max="12" width="15.7019230769231" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.3203125" customWidth="1"/>
+    <col min="5" max="6" width="15.703125" customWidth="1"/>
+    <col min="7" max="8" width="15.703125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15.703125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="15.703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -1532,37 +1535,40 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
       <c r="G1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1" s="6"/>
     </row>
     <row r="2" spans="7:12">
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1570,19 +1576,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
         <v>50</v>
@@ -1611,19 +1617,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1">
         <v>50</v>
@@ -1652,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>8.8</v>
@@ -1690,10 +1696,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1725,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>12.8</v>
@@ -1763,13 +1769,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>12.8</v>
@@ -1801,13 +1807,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>12.8</v>
@@ -1839,13 +1845,13 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>12.8</v>
@@ -1877,13 +1883,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>12.8</v>
@@ -1915,13 +1921,13 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>13.8</v>
@@ -1953,13 +1959,13 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1991,13 +1997,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>15</v>
@@ -2006,7 +2012,7 @@
         <v>50</v>
       </c>
       <c r="H14" s="1">
-        <f>E14*G14/100</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="I14" s="2">
@@ -2029,10 +2035,10 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>15</v>
@@ -2064,13 +2070,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -2102,13 +2108,13 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -2140,13 +2146,13 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>15</v>
@@ -2178,13 +2184,13 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>15</v>
@@ -2216,13 +2222,13 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>15</v>
@@ -2254,13 +2260,13 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>15</v>
@@ -2292,13 +2298,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>15</v>
@@ -2330,13 +2336,13 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>16.8</v>
@@ -2368,13 +2374,13 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>16.8</v>
@@ -2406,13 +2412,13 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>16.8</v>
@@ -2444,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>16.8</v>
@@ -2482,13 +2488,13 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27">
         <v>16.8</v>
@@ -2520,13 +2526,13 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28">
         <v>16.8</v>
@@ -2558,13 +2564,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>18</v>
@@ -2596,13 +2602,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>18</v>
@@ -2634,10 +2640,10 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>18</v>
@@ -2669,13 +2675,13 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>18</v>
@@ -2707,10 +2713,10 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>19.8</v>
@@ -2742,13 +2748,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>19.8</v>
@@ -2780,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35">
         <v>19.8</v>
@@ -2818,13 +2824,13 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>19.8</v>
@@ -2856,13 +2862,13 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37">
         <v>19.8</v>
@@ -2894,13 +2900,13 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38">
         <v>19.8</v>
@@ -2932,13 +2938,13 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39">
         <v>19.8</v>
@@ -2970,13 +2976,13 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40">
         <v>19.8</v>
@@ -3008,13 +3014,13 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41">
         <v>19.8</v>
@@ -3046,13 +3052,13 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42">
         <v>19.8</v>
@@ -3084,13 +3090,13 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43">
         <v>19.8</v>
@@ -3122,13 +3128,13 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44">
         <v>19.8</v>
@@ -3160,13 +3166,13 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>19.8</v>
@@ -3198,13 +3204,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46">
         <v>19.9</v>
@@ -3236,13 +3242,13 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>15</v>
@@ -3274,13 +3280,13 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E48">
         <v>22.8</v>
@@ -3312,13 +3318,13 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49">
         <v>24.8</v>
@@ -3350,13 +3356,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50">
         <v>24.8</v>
@@ -3388,13 +3394,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51">
         <v>25</v>
@@ -3426,13 +3432,13 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52">
         <v>25</v>
@@ -3464,13 +3470,13 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53">
         <v>25</v>
@@ -3502,13 +3508,13 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54">
         <v>25</v>
@@ -3540,13 +3546,13 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55">
         <v>25</v>
@@ -3578,13 +3584,13 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56">
         <v>25</v>
@@ -3616,13 +3622,13 @@
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E57">
         <v>25</v>
@@ -3654,13 +3660,13 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58">
         <v>25</v>
@@ -3692,19 +3698,19 @@
         <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59">
         <v>25</v>
       </c>
       <c r="F59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G59" s="1">
         <v>50</v>
@@ -3733,13 +3739,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60">
         <v>25</v>
@@ -3771,13 +3777,13 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61">
         <v>26.8</v>
@@ -3809,13 +3815,13 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62">
         <v>26.8</v>
@@ -3847,13 +3853,13 @@
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63">
         <v>26.8</v>
@@ -3885,13 +3891,13 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>28</v>
@@ -3923,13 +3929,13 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65">
         <v>20</v>
@@ -3961,13 +3967,13 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66">
         <v>29</v>
@@ -3999,13 +4005,13 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67">
         <v>29.8</v>
@@ -4037,13 +4043,13 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68">
         <v>29.8</v>
@@ -4075,13 +4081,13 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69">
         <v>29.8</v>
@@ -4113,19 +4119,19 @@
         <v>6</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70">
         <v>29.8</v>
       </c>
       <c r="F70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G70" s="1">
         <v>50</v>
@@ -4154,13 +4160,13 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E71">
         <v>25</v>
@@ -4192,13 +4198,13 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72">
         <v>35</v>
@@ -4230,10 +4236,10 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73">
         <v>35</v>
@@ -4265,13 +4271,13 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74">
         <v>35</v>
@@ -4303,13 +4309,13 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75">
         <v>35</v>
@@ -4341,13 +4347,13 @@
         <v>6</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76">
         <v>35</v>
@@ -4379,19 +4385,19 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77">
         <v>35</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G77" s="1">
         <v>50</v>
@@ -4420,13 +4426,13 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78">
         <v>38</v>
@@ -4458,19 +4464,19 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79">
         <v>45</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G79" s="1">
         <v>50</v>
@@ -4499,13 +4505,13 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E80">
         <v>38</v>
@@ -4537,13 +4543,13 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81">
         <v>48</v>
@@ -4575,13 +4581,13 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82">
         <v>58</v>
@@ -4613,13 +4619,13 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83">
         <v>68</v>
@@ -4651,13 +4657,13 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84">
         <v>68</v>
@@ -4689,13 +4695,13 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85">
         <v>68</v>
@@ -4727,13 +4733,13 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D86" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E86">
         <v>58</v>
@@ -4765,13 +4771,13 @@
         <v>5</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>68</v>
@@ -4803,13 +4809,13 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>58</v>
@@ -4841,13 +4847,13 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -4879,13 +4885,13 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E90">
         <v>88</v>
@@ -4917,13 +4923,13 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E91">
         <v>78</v>
@@ -4955,13 +4961,13 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E92">
         <v>99</v>
@@ -4993,13 +4999,13 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E93">
         <v>88</v>
@@ -5031,13 +5037,13 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E94">
         <v>88</v>
@@ -5069,13 +5075,13 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>99</v>
@@ -5107,13 +5113,13 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E96">
         <v>108</v>
@@ -5145,13 +5151,13 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E97">
         <v>128</v>
@@ -5183,13 +5189,13 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E98">
         <v>168</v>
@@ -5221,13 +5227,13 @@
         <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E99">
         <v>168</v>
@@ -5259,13 +5265,13 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E100">
         <v>168</v>
@@ -5297,13 +5303,13 @@
         <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E101">
         <v>188</v>
@@ -5332,13 +5338,13 @@
     </row>
     <row r="102" spans="7:11">
       <c r="G102" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
